--- a/output/pdf_financials_xlsx/GZD.xlsx
+++ b/output/pdf_financials_xlsx/GZD.xlsx
@@ -919,49 +919,49 @@
         <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>1.047613</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>6.712123</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>0.665929</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>0.705541</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>0.237199</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>3.201437</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>0.256262</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>1.915393</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>0.367798</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>0.171177</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>0.496899</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>0.587553</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>1.09087</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>0.621961</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0</v>
+        <v>0.410836</v>
       </c>
     </row>
     <row r="11">
@@ -977,49 +977,49 @@
         <v>0</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>-1.047613</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>-6.712123</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>-0.665929</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0</v>
+        <v>-0.705541</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0</v>
+        <v>-0.237199</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0</v>
+        <v>-3.201437</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>-0.256262</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
+        <v>-1.915393</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0</v>
+        <v>-0.367798</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0</v>
+        <v>-0.171177</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0</v>
+        <v>-0.496899</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0</v>
+        <v>-0.587553</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0</v>
+        <v>-1.09087</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0</v>
+        <v>-0.621961</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0</v>
+        <v>-0.410836</v>
       </c>
     </row>
     <row r="12">
@@ -1035,49 +1035,49 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.034436</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.03818</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.00556</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.011297</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002398</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.00094</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000753</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.001797</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.002193</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.00203</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.002687</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.011267</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.033211</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.009393</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.002868</v>
       </c>
     </row>
     <row r="13">
@@ -2015,49 +2015,49 @@
         <v>-0.727579</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.827483</v>
+        <v>-0.861919</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-6.458123</v>
+        <v>-6.496303</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.660369</v>
+        <v>-0.665929</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.694244</v>
+        <v>-0.705541</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.234801</v>
+        <v>-0.237199</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-3.19176</v>
+        <v>-3.1927</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.255509</v>
+        <v>-0.256262</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.913596</v>
+        <v>-1.915393</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.361605</v>
+        <v>-0.363798</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.15877</v>
+        <v>-0.1608</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.364164</v>
+        <v>-0.366851</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.435292</v>
+        <v>-0.446559</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.7355660000000001</v>
+        <v>-0.768777</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.582063</v>
+        <v>-0.591456</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.402951</v>
+        <v>-0.405819</v>
       </c>
     </row>
     <row r="28">
@@ -2131,49 +2131,49 @@
         <v>-0.727579</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.821164</v>
+        <v>-0.8556</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-6.44738</v>
+        <v>-6.48556</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.652849</v>
+        <v>-0.658409</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.68898</v>
+        <v>-0.700277</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.231117</v>
+        <v>-0.233515</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.190424</v>
+        <v>-3.191364</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.255509</v>
+        <v>-0.256262</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.913596</v>
+        <v>-1.915393</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.361605</v>
+        <v>-0.363798</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.15877</v>
+        <v>-0.1608</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.364164</v>
+        <v>-0.366851</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.435292</v>
+        <v>-0.446559</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.7355660000000001</v>
+        <v>-0.768777</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.582063</v>
+        <v>-0.591456</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.402951</v>
+        <v>-0.405819</v>
       </c>
     </row>
     <row r="30">
@@ -27042,7 +27042,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -27061,46 +27061,46 @@
         </is>
       </c>
       <c r="H191" s="5" t="n">
-        <v>-6.712123</v>
+        <v>6.712123</v>
       </c>
       <c r="I191" s="5" t="n">
-        <v>-0.665929</v>
+        <v>0.665929</v>
       </c>
       <c r="J191" s="5" t="n">
-        <v>-0.705541</v>
+        <v>0.705541</v>
       </c>
       <c r="K191" s="5" t="n">
-        <v>-0.237199</v>
+        <v>0.237199</v>
       </c>
       <c r="L191" s="5" t="n">
-        <v>-3.201437</v>
+        <v>3.201437</v>
       </c>
       <c r="M191" s="5" t="n">
-        <v>-0.256262</v>
+        <v>0.256262</v>
       </c>
       <c r="N191" s="5" t="n">
-        <v>-1.915393</v>
+        <v>1.915393</v>
       </c>
       <c r="O191" s="5" t="n">
-        <v>-0.367798</v>
+        <v>0.367798</v>
       </c>
       <c r="P191" s="5" t="n">
-        <v>-0.171177</v>
+        <v>0.171177</v>
       </c>
       <c r="Q191" s="5" t="n">
-        <v>-0.496899</v>
+        <v>0.496899</v>
       </c>
       <c r="R191" s="5" t="n">
-        <v>-0.587553</v>
+        <v>0.587553</v>
       </c>
       <c r="S191" s="5" t="n">
-        <v>-1.09087</v>
+        <v>1.09087</v>
       </c>
       <c r="T191" s="5" t="n">
-        <v>-0.621961</v>
+        <v>0.621961</v>
       </c>
       <c r="U191" s="5" t="n">
-        <v>-0.410836</v>
+        <v>0.410836</v>
       </c>
     </row>
     <row r="192">
@@ -27220,7 +27220,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -28469,7 +28469,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -30709,7 +30709,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -30753,10 +30753,10 @@
         </is>
       </c>
       <c r="M228" s="5" t="n">
-        <v>-0.256262</v>
+        <v>0.256262</v>
       </c>
       <c r="N228" s="5" t="n">
-        <v>-1.915393</v>
+        <v>1.915393</v>
       </c>
       <c r="O228" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -31622,7 +31622,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -31651,10 +31651,10 @@
         </is>
       </c>
       <c r="J237" s="5" t="n">
-        <v>-0.705541</v>
+        <v>0.705541</v>
       </c>
       <c r="K237" s="5" t="n">
-        <v>-0.237199</v>
+        <v>0.237199</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -33836,7 +33836,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -33850,10 +33850,10 @@
         </is>
       </c>
       <c r="G259" s="5" t="n">
-        <v>-1.047613</v>
+        <v>1.047613</v>
       </c>
       <c r="H259" s="5" t="n">
-        <v>-6.712123</v>
+        <v>6.712123</v>
       </c>
       <c r="I259" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GZD.xlsx
+++ b/output/pdf_financials_xlsx/GZD.xlsx
@@ -18381,7 +18381,11 @@
           <t>Proceeds from private placement (note 8)</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
